--- a/nao_positivados_03-2026.xlsx
+++ b/nao_positivados_03-2026.xlsx
@@ -21573,7 +21573,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>ESPUM CASA PERINI AQUARELA ROSE 750ML</t>
+          <t>ESPUM CASA PERINI BRUT 750ML</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -30773,7 +30773,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>4 PACK RED BULL MELÃO C/ MARACUJA</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -51358,7 +51358,7 @@
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL TROPICAL 4X250ML</t>
         </is>
       </c>
       <c r="E1505" t="inlineStr">
@@ -63914,7 +63914,7 @@
       </c>
       <c r="D1877" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL ZERO</t>
+          <t>MOVING HYDRO PROTEIN F VERMELHA 12X500ML</t>
         </is>
       </c>
       <c r="E1877" t="inlineStr">
@@ -64697,7 +64697,7 @@
       </c>
       <c r="D1900" t="inlineStr">
         <is>
-          <t>ST PIERRE VIDRO PINK LIMONADE LN 275X12</t>
+          <t>NECTAR LARANJA 12X1000ML</t>
         </is>
       </c>
       <c r="E1900" t="inlineStr">
@@ -88729,7 +88729,7 @@
       </c>
       <c r="D2604" t="inlineStr">
         <is>
-          <t>ESPUMANTE ALUD ROSE 750ML</t>
+          <t>ESPUMANTE ALUD BRANCO 750ML</t>
         </is>
       </c>
       <c r="E2604" t="inlineStr">

--- a/nao_positivados_03-2026.xlsx
+++ b/nao_positivados_03-2026.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NECTAR GOIABA 12X1000ML</t>
+          <t>MOVING JUICE PROTEIN LARANJA 12X300ML</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>GUARAVITON GINSENG 12X500ML</t>
+          <t>GUARAVITA NATURAL 24X290ML</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RED BULL CEREJA 24X250ML</t>
+          <t>RED BULL SUGAR FREE 24X250ML</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL SF NECTARINA 4X250ML</t>
+          <t>4 PACK RED BULL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
+          <t>PINATI SIMPLE WHEY PISTACHE 16X35G</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VODKA ABSOLUT CX C/ 12X50ML</t>
+          <t>GIN BEEFEATER CX C/ 12X50ML</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SAKE AZUMA KIRIN COMUM 600ML</t>
+          <t>LICOR COINTREAU 700 ML</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7727,7 +7727,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>94091</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>LEBLON</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>94091</t>
+          <t>94092</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LEBLON</t>
+          <t>SÃO CONRADO</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>94092</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SÃO CONRADO</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>CACHACA YPIOCA CG PRATA 965 ML</t>
+          <t>ESPUM CASA PERINI BRUT 750ML</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>GIN ROCKS 1000ML</t>
+          <t>GIN ROCKS STRAWBERRY 1000ML</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>SUCO DE UVA TTO INT QNT DO MORGADO 1,5L</t>
+          <t>NECTAR MISTO UVA E PERA 12X1000ML</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>AGUA MINERAL MINALBA C/ GAS 12X510ML</t>
+          <t>AGUA MINERAL MINALBA S/ GAS 6X1,5L</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>GUARAVITA NATURAL 24X290ML</t>
+          <t>4 PACK RED BULL</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>ESPUM CASA PERINI BRUT ROSE 750ML</t>
+          <t>ESPUM CASA PERINI AQUARELA ROSE 750ML</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>AGUA MINERAL MINALBA S/ GAS 6X1,5L</t>
+          <t>AGUA MINERAL MINALBA S/ GAS 12X510ML</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>COQUETEL PINK MOON 12X600ML - PET</t>
+          <t>AGUA MINALBA C/ GAS 6X1,5L</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -14278,7 +14278,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>93384</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SANTISSIMO</t>
+          <t>CAMPO GRANDE</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -14311,7 +14311,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>93383</t>
+          <t>93384</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CAMPO GRANDE</t>
+          <t>SANTISSIMO</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -19802,7 +19802,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>90406</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -19812,12 +19812,12 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>LARGO DA BATALHA</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>WHISKY JIM BEAM WHITE 1L</t>
+          <t>WHISKY JIM BEAM APPLE 1L</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -19825,7 +19825,11 @@
           <t>DANIELLE MOURA - OFF TRADE</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr"/>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>DANIELLE MOURA - OFF TRADE</t>
+        </is>
+      </c>
       <c r="G576" t="inlineStr">
         <is>
           <t>25/02/2026</t>
@@ -19835,7 +19839,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>90406</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -19845,7 +19849,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>LARGO DA BATALHA</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -19858,11 +19862,7 @@
           <t>DANIELLE MOURA - OFF TRADE</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>DANIELLE MOURA - OFF TRADE</t>
-        </is>
-      </c>
+      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
           <t>25/02/2026</t>
@@ -19872,7 +19872,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>90410</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>ENGENHO DO MATO</t>
+          <t>VIGA</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -19895,11 +19895,7 @@
           <t>DANIELLE MOURA - OFF TRADE</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>DANIELLE MOURA - OFF TRADE</t>
-        </is>
-      </c>
+      <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr">
         <is>
           <t>23/02/2026</t>
@@ -19909,7 +19905,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -19919,7 +19915,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>VIGA</t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -19932,7 +19928,11 @@
           <t>DANIELLE MOURA - OFF TRADE</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>DANIELLE MOURA - OFF TRADE</t>
+        </is>
+      </c>
       <c r="G579" t="inlineStr">
         <is>
           <t>23/02/2026</t>
@@ -19942,7 +19942,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>90414</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>VALVERDE</t>
+          <t>INHAUMA</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -19979,7 +19979,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>90414</t>
+          <t>90410</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -19989,12 +19989,12 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>INHAUMA</t>
+          <t>ENGENHO DO MATO</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>WHISKY JIM BEAM HONEY 1L</t>
+          <t>WHISKY JIM BEAM WHITE 1L</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -20016,7 +20016,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>91842</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -20026,12 +20026,12 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>LOTE XV</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>WHISKY JIM BEAM APPLE 1L</t>
+          <t>WHISKY JIM BEAM BLACK CHERRY 1L</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -20049,7 +20049,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>LOTE XV</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>WHISKY JIM BEAM APPLE 1L</t>
+          <t>WHISKY JIM BEAM BLACK CHERRY 1L</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>VEJA MULTIUSO/1BAN/1COZ PACK C/3 24X500M</t>
+          <t>VEJA PERF LIRIO NILO 24X500ML</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -21573,7 +21573,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>ESPUM CASA PERINI BRUT 750ML</t>
+          <t>APERITIVO APEROL 750 ML</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>MOVING HYDRO PROTEIN UVA 12X500ML</t>
+          <t>MOVING HYDRO PROTEIN LIMAO 12X500ML</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>NECTAR MANGA 12X1000ML</t>
+          <t>MOVING HYDRO PROTEIN TANGERINA 12X500ML</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>MOVING HYDRO PROTEIN LIMAO 12X500ML</t>
+          <t>MOVING HYDRO PROTEIN F VERMELHA 12X500ML</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>CHICLETE TRIDENT MORANGO C/21 UN</t>
+          <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>BALA HALLS CEREJA C/21 UND</t>
+          <t>VEJA PERF 2L FLORES DO MEDITERR PROMO</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>RANCHEIRO RECHEADO BAUNILHA 90G</t>
+          <t>RANCHEIRO ROSQ 500G COCO</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>NG BARRA NEUGE 80G AMENDOLATE (DP 16X80G</t>
+          <t>NG BARRA NEUGE 80G P&amp;B (DP 16X80G)</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>ST PIERRE ZERO LATA GUARANA  LT 24X310ML</t>
+          <t>ST PIERRE ZERO LATA TROPICAL LT 24X310ML</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -27685,7 +27685,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>NG BARRA NEUGE 80G P&amp;B (DP 16X80G)</t>
+          <t>NG BARRA 80G 40% MEIO AMARGO (DP 16X80G)</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>RANCHEIRO  RECHEADO MORANGO 90G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -29076,7 +29076,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>85418</t>
+          <t>85416</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -29086,12 +29086,12 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>SANTA LÚCIA</t>
+          <t>ILHA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>PINATI DOUBLE BAR BRIGADEIRO 32X35G</t>
+          <t>PINATI NUTS ZERO COCO 16X4X25G</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -29109,7 +29109,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>85419</t>
+          <t>85414</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -29119,7 +29119,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>JARDIM CAMBURI</t>
+          <t>BRISAMAR</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -29142,7 +29142,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>85420</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>JARDIM DA PENHA</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>PINATI NUTS COCO 16X4X25G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
@@ -29175,7 +29175,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>85420</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -29185,12 +29185,12 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>CONSOLAÇÃO</t>
+          <t>JARDIM DA PENHA</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -29208,7 +29208,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>85417</t>
+          <t>85425</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -29218,12 +29218,12 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>JARDIM CAMBURI</t>
+          <t>CONSOLAÇÃO</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>PINATI NUTS ZERO ORIGINAL 16X4X25G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -29241,7 +29241,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>85416</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -29251,12 +29251,12 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>ILHA DE SANTA MARIA</t>
+          <t>JARDIM CAMBURI</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI NUTS ZERO ORIGINAL 16X4X25G</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -29274,7 +29274,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>85413</t>
+          <t>85418</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -29284,12 +29284,12 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>ARIBIRI</t>
+          <t>SANTA LÚCIA</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI NUTS BANANA 16X4X120G</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -29307,7 +29307,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>85414</t>
+          <t>85413</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -29317,12 +29317,12 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>BRISAMAR</t>
+          <t>ARIBIRI</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -29340,7 +29340,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t>85419</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDIM CAMBURI</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -29406,7 +29406,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>85405</t>
+          <t>91293</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -29416,12 +29416,12 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>CIVIT II</t>
+          <t>MARCÍLIO DE NORONHA</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>PINATI NUTS COCO 20X30G</t>
+          <t>PINATI SLIM WHEY BEIJINHO 16X35G</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -29439,7 +29439,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -29449,12 +29449,12 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>MARACANA</t>
+          <t>CIVIT II</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>PINATI DOUBLE BAR BANANA AMENDOIM 32X35G</t>
+          <t>PINATI NUTS COCO 20X30G</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -29472,7 +29472,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>85428</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -29482,12 +29482,12 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>MARACANA</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -29505,7 +29505,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>91293</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -29515,12 +29515,12 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>MARCÍLIO DE NORONHA</t>
+          <t>SAO FRANCISCO</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 16X4X120G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL SUGAR FREE</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>MOVING HYDRO PROTEIN TANGERINA 12X500ML</t>
+          <t>MOVING PROTEIN AGUA DE COCO 12X300ML</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>GUARAVITA NATURAL 24X290ML</t>
+          <t>GUARAVITON GINSENG 12X500ML</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL ZERO</t>
+          <t>4 PACK RED BULL</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -30551,7 +30551,7 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL MORANGO PESSEGO</t>
+          <t>RED BULL TROPICAL 24X250ML</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -30721,7 +30721,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>79021</t>
+          <t>80672</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -30758,7 +30758,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>79021</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -30773,7 +30773,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL MELÃO C/ MARACUJA</t>
+          <t>RED BULL MELANCIA 250ML CX C/24</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
@@ -30810,7 +30810,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL MELANCIA</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -31420,7 +31420,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL ZERO</t>
+          <t>CHICLETE TRIDENT MENTA C/21 UN</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -32847,7 +32847,7 @@
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>BALA HALLS MELANCIA C/21 UND</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -32979,7 +32979,7 @@
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>AZEITE DE OLIVA EV ESSENZA 5L</t>
+          <t>CHICLETE TRIDENT HORTELA C/21 UN</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RC SARDINHA EM OLEO 125G</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>BALA HALLS 21S MENTA PRATA NEW</t>
+          <t>NG BARRA NEUGE 80G COOKIES BRANCO (DP 16</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -33837,7 +33837,7 @@
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>ESPUMANTE ALUD BRANCO 750ML</t>
+          <t>ESPUMANTE ALUD ROSE 750ML</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -34119,7 +34119,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -34129,12 +34129,12 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>JARDIM CARAPINA</t>
+          <t>NOVA BETHANIA</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY PISTACHE 16X35G</t>
+          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -34185,7 +34185,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -34195,12 +34195,12 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>NOVA BETHANIA</t>
+          <t>JARDIM CARAPINA</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
+          <t>PINATI SIMPLE WHEY PISTACHE 16X35G</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -34365,7 +34365,7 @@
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>PINATI DB WHEY FRAPE DE COCO 12X50G</t>
+          <t>PINATI SWEET COCADINHA CHOCO 24X14G</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -34661,7 +34661,7 @@
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>GIN ROCKS 1000ML</t>
+          <t>VODCA SMIRNOFF RED 998 ML</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>VODCA SMIRNOFF RED 998 ML</t>
+          <t>SMIRNOFF ICE - 24 UNIDADES (LONG NECK)</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>XAROPE MONIN MACA VERDE (APPLE) 700 ML</t>
+          <t>RED BULL SF BLUEBERRY BAUNILHA  24X250ML</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
@@ -35879,7 +35879,7 @@
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL MELANCIA 250ML CX C/24</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
@@ -35953,7 +35953,7 @@
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>WHISKY JACK DANIELS FIRE 1000 ML</t>
+          <t>RUM MONTILLA CARTA BRANCA 1000ML</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
@@ -37861,7 +37861,7 @@
       </c>
       <c r="D1108" t="inlineStr">
         <is>
-          <t>VINHO BCO ARCAIA PINOT GRIGIO 750ML</t>
+          <t>HUMB. CANALE DENARIO SAUV. BLANC</t>
         </is>
       </c>
       <c r="E1108" t="inlineStr">
@@ -37935,7 +37935,7 @@
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>WHISKY JIM BEAM WHITE 1L</t>
+          <t>CACHACA VELHO BARREIRO 910 ML</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
@@ -40180,7 +40180,7 @@
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL SUGAR FREE 24X250ML</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
@@ -41227,7 +41227,7 @@
       </c>
       <c r="D1202" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>4 PACK RED BULL TROPICAL 4X250ML</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
@@ -42060,7 +42060,7 @@
       </c>
       <c r="D1227" t="inlineStr">
         <is>
-          <t>RC SARDINHA EM OLEO 125G</t>
+          <t>RED BULL MELANCIA 250ML CX C/24</t>
         </is>
       </c>
       <c r="E1227" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
+          <t>CHICLETE TRIDENT MELANCIA C/21 UN</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
@@ -42192,7 +42192,7 @@
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL MORANGO PESSEGO</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
@@ -43017,7 +43017,7 @@
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL ZERO  24X250ML</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
@@ -43083,7 +43083,7 @@
       </c>
       <c r="D1258" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL ZERO</t>
+          <t>4 PACK RED BULL SUGAR FREE</t>
         </is>
       </c>
       <c r="E1258" t="inlineStr">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>WHISKY JACK DANIELS 1L</t>
+          <t>GIN BEEFEATER 750ML</t>
         </is>
       </c>
       <c r="E1270" t="inlineStr">
@@ -43710,7 +43710,7 @@
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
+          <t>CHICLETE TRIDENT MENTA C/21 UN</t>
         </is>
       </c>
       <c r="E1277" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="D1302" t="inlineStr">
         <is>
-          <t>NG MUMU KIDS 15,6G COCO (DP 24X15,6G)</t>
+          <t>NG MUMU KIDS 15,6G BAUNILHA (DP 24X15,6G</t>
         </is>
       </c>
       <c r="E1302" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="D1307" t="inlineStr">
         <is>
-          <t>NG BIBS 720G AO LEITE (DP 18X40G)</t>
+          <t>RANCHEIRO  RECHEADO MORANGO 90G</t>
         </is>
       </c>
       <c r="E1307" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="D1308" t="inlineStr">
         <is>
-          <t>RANCHEIRO  RECHEADO MORANGO 90G</t>
+          <t>NG DOCE DE LEITE MUMU 350G</t>
         </is>
       </c>
       <c r="E1308" t="inlineStr">
@@ -45137,7 +45137,7 @@
       </c>
       <c r="D1320" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN RET 24X600ML</t>
+          <t>CERVEJA HEINEKEN 473ML (LATAO) - 12 UNID</t>
         </is>
       </c>
       <c r="E1320" t="inlineStr">
@@ -45471,7 +45471,7 @@
       </c>
       <c r="D1330" t="inlineStr">
         <is>
-          <t>RED BULL ZERO  24X250ML</t>
+          <t>GIN ROCKS STRAWBERRY 1000ML</t>
         </is>
       </c>
       <c r="E1330" t="inlineStr">
@@ -45801,7 +45801,7 @@
       </c>
       <c r="D1340" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN LONG 330ML</t>
+          <t>CERVEJA HEINEKEN 473ML (LATAO) - 12 UNID</t>
         </is>
       </c>
       <c r="E1340" t="inlineStr">
@@ -46168,7 +46168,7 @@
       </c>
       <c r="D1351" t="inlineStr">
         <is>
-          <t>GUARAVITON GINSENG 12X500ML</t>
+          <t>MOVING BOOSTER ABACAXI HORTELA 24X310ML</t>
         </is>
       </c>
       <c r="E1351" t="inlineStr">
@@ -47669,7 +47669,7 @@
       </c>
       <c r="D1396" t="inlineStr">
         <is>
-          <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
+          <t>RANCHEIRO RECHEADO BAUNILHA 90G</t>
         </is>
       </c>
       <c r="E1396" t="inlineStr">
@@ -49287,7 +49287,7 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
@@ -49297,7 +49297,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>PORTO DE SANTANA</t>
+          <t>CAMPO GRANDE</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
@@ -49320,7 +49320,7 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>81678</t>
+          <t>81690</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>CAMPO GRANDE</t>
+          <t>PORTO DE SANTANA</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -49353,7 +49353,7 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>81679</t>
+          <t>81696</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -49363,12 +49363,12 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>FLEXAL I</t>
+          <t>PORTO NOVO</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
         <is>
-          <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
+          <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
         </is>
       </c>
       <c r="E1447" t="inlineStr">
@@ -49386,7 +49386,7 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>81681</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -49396,7 +49396,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>ITACIBA</t>
+          <t>FLEXAL I</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -49419,7 +49419,7 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>81677</t>
+          <t>81681</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
@@ -49429,12 +49429,12 @@
       </c>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>ITACIBA</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
         <is>
-          <t>NG BARRA NEUGE 80G BRANCO (DP 16X80G)</t>
+          <t>NG BARRA NEUGE 80G AO LEITE (DP 16X80G)</t>
         </is>
       </c>
       <c r="E1449" t="inlineStr">
@@ -49452,7 +49452,7 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>81696</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
@@ -49462,7 +49462,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>PORTO NOVO</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -51358,7 +51358,7 @@
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL TROPICAL 4X250ML</t>
+          <t>4 PACK RED BULL MELANCIA</t>
         </is>
       </c>
       <c r="E1505" t="inlineStr">
@@ -52389,7 +52389,7 @@
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>BALA HALLS MORANGO C/21 UND</t>
+          <t>NG AMOR CARIOCA BOMBOM 200G (10X20G)</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
@@ -52422,7 +52422,7 @@
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL MORANGO PESSEGO</t>
+          <t>4 PACK RED BULL TROPICAL 4X250ML</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
@@ -52554,7 +52554,7 @@
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI NUTS ORIGINAL 20X30G</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
@@ -55029,7 +55029,7 @@
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>PINATI NUTS ORIGINAL 16X4X30G</t>
+          <t>PINATI NUTS BANANA 20X30G</t>
         </is>
       </c>
       <c r="E1616" t="inlineStr">
@@ -56034,7 +56034,7 @@
       </c>
       <c r="D1645" t="inlineStr">
         <is>
-          <t>NG MUMU KIDS SORTIDO 30X187,20G</t>
+          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
         </is>
       </c>
       <c r="E1645" t="inlineStr">
@@ -56809,7 +56809,7 @@
       </c>
       <c r="D1668" t="inlineStr">
         <is>
-          <t>RANCHEIRO ROSQ 500G COCO</t>
+          <t>RANCHEIRO ROSQ 300G CHOCOLATE</t>
         </is>
       </c>
       <c r="E1668" t="inlineStr">
@@ -56978,7 +56978,7 @@
       </c>
       <c r="D1673" t="inlineStr">
         <is>
-          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
+          <t>PINATI SLIM WHEY BRIGADEIRO 16X35G</t>
         </is>
       </c>
       <c r="E1673" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>PINATI DOUBLE BAR BANANA AMENDOIM 32X35G</t>
+          <t>PINATI SIMPLE WHEY CHOCO BELGA 16X35G</t>
         </is>
       </c>
       <c r="E1674" t="inlineStr">
@@ -58625,7 +58625,7 @@
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>84011</t>
+          <t>84012</t>
         </is>
       </c>
       <c r="B1723" t="inlineStr">
@@ -58635,12 +58635,12 @@
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>ESPUM CASA PERINI AQUARELA ROSE 750ML</t>
+          <t>ESPUM CASA PERINI BRUT 750ML</t>
         </is>
       </c>
       <c r="E1723" t="inlineStr">
@@ -58658,7 +58658,7 @@
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>84012</t>
+          <t>84014</t>
         </is>
       </c>
       <c r="B1724" t="inlineStr">
@@ -58668,12 +58668,12 @@
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>SESSENTA</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>ESPUM CASA PERINI BRUT 750ML</t>
+          <t>WHISKY JIM BEAM BLACK CHERRY 1L</t>
         </is>
       </c>
       <c r="E1724" t="inlineStr">
@@ -58691,7 +58691,7 @@
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>84014</t>
+          <t>84011</t>
         </is>
       </c>
       <c r="B1725" t="inlineStr">
@@ -58701,7 +58701,7 @@
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>SESSENTA</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
@@ -59246,7 +59246,7 @@
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>VODKA SMIRNOFF 600 ML</t>
+          <t>GUARAVITA NATURAL 24X290ML</t>
         </is>
       </c>
       <c r="E1741" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t>AGUA NA CAIXA 12X500ML</t>
+          <t>AGUA NA CAIXA 12X330ML</t>
         </is>
       </c>
       <c r="E1778" t="inlineStr">
@@ -61134,7 +61134,7 @@
       </c>
       <c r="D1797" t="inlineStr">
         <is>
-          <t>GUARAVITON GINSENG 12X500ML</t>
+          <t>GUARAVITA NATURAL 24X290ML</t>
         </is>
       </c>
       <c r="E1797" t="inlineStr">
@@ -61373,7 +61373,7 @@
       </c>
       <c r="D1804" t="inlineStr">
         <is>
-          <t>AGUA PERRIER C/ GAS 24X330ML</t>
+          <t>MOVING HYDRO PROTEIN LIMAO 12X500ML</t>
         </is>
       </c>
       <c r="E1804" t="inlineStr">
@@ -61447,7 +61447,7 @@
       </c>
       <c r="D1806" t="inlineStr">
         <is>
-          <t>AGUA MINERAL MINALBA C/ GAS 12X510ML</t>
+          <t>AGUA MINERAL MINALBA S/ GAS 12X510ML</t>
         </is>
       </c>
       <c r="E1806" t="inlineStr">
@@ -62592,7 +62592,7 @@
       </c>
       <c r="D1839" t="inlineStr">
         <is>
-          <t>GIN BOMBAY SAPPHIRE 750ML</t>
+          <t>VODCA SMIRNOFF RED 998 ML</t>
         </is>
       </c>
       <c r="E1839" t="inlineStr">
@@ -63062,7 +63062,7 @@
       </c>
       <c r="D1853" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350 ML (SLEEK) 12 UNID</t>
+          <t>GUARAVITA NATURAL 24X290ML</t>
         </is>
       </c>
       <c r="E1853" t="inlineStr">
@@ -63132,7 +63132,7 @@
       </c>
       <c r="D1855" t="inlineStr">
         <is>
-          <t>GIN GORDONS 750 ML</t>
+          <t>CERVEJA HEINEKEN 350 ML (SLEEK) 12 UNID</t>
         </is>
       </c>
       <c r="E1855" t="inlineStr">
@@ -63655,7 +63655,7 @@
       </c>
       <c r="D1870" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL TROPICAL 24X250ML</t>
         </is>
       </c>
       <c r="E1870" t="inlineStr">
@@ -63914,7 +63914,7 @@
       </c>
       <c r="D1877" t="inlineStr">
         <is>
-          <t>MOVING HYDRO PROTEIN F VERMELHA 12X500ML</t>
+          <t>4 PACK RED BULL ZERO</t>
         </is>
       </c>
       <c r="E1877" t="inlineStr">
@@ -64099,7 +64099,7 @@
       </c>
       <c r="D1882" t="inlineStr">
         <is>
-          <t>COQUETEL PINK MOON 12X600ML - PET</t>
+          <t>NECTAR MANGA 12X1000ML</t>
         </is>
       </c>
       <c r="E1882" t="inlineStr">
@@ -64165,7 +64165,7 @@
       </c>
       <c r="D1884" t="inlineStr">
         <is>
-          <t>COQUETEL BANANINHA REGGIANI 950ML</t>
+          <t>ST PIERRE LATA PINK LEMON LT 24X270ML</t>
         </is>
       </c>
       <c r="E1884" t="inlineStr">
@@ -64697,7 +64697,7 @@
       </c>
       <c r="D1900" t="inlineStr">
         <is>
-          <t>NECTAR LARANJA 12X1000ML</t>
+          <t>ST PIERRE VIDRO PINK LIMONADE LN 275X12</t>
         </is>
       </c>
       <c r="E1900" t="inlineStr">
@@ -66896,7 +66896,7 @@
       </c>
       <c r="D1963" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>GIN ROCKS 1000ML</t>
         </is>
       </c>
       <c r="E1963" t="inlineStr">
@@ -68393,7 +68393,7 @@
       </c>
       <c r="D2004" t="inlineStr">
         <is>
-          <t>GIN BEEFEATER CX C/ 12X50ML</t>
+          <t>TANQUERAY SEVILLA  CX C/ 12X50ML</t>
         </is>
       </c>
       <c r="E2004" t="inlineStr">
@@ -68825,7 +68825,7 @@
       </c>
       <c r="D2016" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL SUGAR FREE 24X250ML</t>
         </is>
       </c>
       <c r="E2016" t="inlineStr">
@@ -68969,7 +68969,7 @@
       </c>
       <c r="D2020" t="inlineStr">
         <is>
-          <t>CACHACA VELHO BARREIRO 910 ML</t>
+          <t>VODCA SMIRNOFF RED 998 ML</t>
         </is>
       </c>
       <c r="E2020" t="inlineStr">
@@ -69039,7 +69039,7 @@
       </c>
       <c r="D2022" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL ZERO  24X250ML</t>
         </is>
       </c>
       <c r="E2022" t="inlineStr">
@@ -69915,7 +69915,7 @@
       </c>
       <c r="D2046" t="inlineStr">
         <is>
-          <t>ICE 51 FRUIT LONG NECK 24X275 ML</t>
+          <t>WHISKY BALLANTINE'S FINEST 1L</t>
         </is>
       </c>
       <c r="E2046" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="D2056" t="inlineStr">
         <is>
-          <t>ZIN TONICA 12X310ML</t>
+          <t>RED BULL MELANCIA 250ML CX C/24</t>
         </is>
       </c>
       <c r="E2056" t="inlineStr">
@@ -71009,7 +71009,7 @@
       </c>
       <c r="D2076" t="inlineStr">
         <is>
-          <t>PINATI NUTS BANANA 20X30G</t>
+          <t>PINATI NUTS COCO 20X30G</t>
         </is>
       </c>
       <c r="E2076" t="inlineStr">
@@ -72902,7 +72902,7 @@
       </c>
       <c r="D2133" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL SUGAR FREE 24X250ML</t>
         </is>
       </c>
       <c r="E2133" t="inlineStr">
@@ -74960,7 +74960,7 @@
       </c>
       <c r="D2195" t="inlineStr">
         <is>
-          <t>MARTINI ROSSO 750 ML</t>
+          <t>MARTINI BIANCO 750 ML</t>
         </is>
       </c>
       <c r="E2195" t="inlineStr">
@@ -75356,7 +75356,7 @@
       </c>
       <c r="D2207" t="inlineStr">
         <is>
-          <t>XAROPE FABBRI MACA VERDE 1L</t>
+          <t>XAROPE FABBRI LIMAO SICILIANO 1L</t>
         </is>
       </c>
       <c r="E2207" t="inlineStr">
@@ -76298,7 +76298,7 @@
     <row r="2236">
       <c r="A2236" t="inlineStr">
         <is>
-          <t>87088</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="B2236" t="inlineStr">
@@ -76331,7 +76331,7 @@
     <row r="2237">
       <c r="A2237" t="inlineStr">
         <is>
-          <t>90559</t>
+          <t>90560</t>
         </is>
       </c>
       <c r="B2237" t="inlineStr">
@@ -76341,12 +76341,12 @@
       </c>
       <c r="C2237" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>AGUA LIMPA</t>
         </is>
       </c>
       <c r="D2237" t="inlineStr">
         <is>
-          <t>RC ATUM RALADO EM OLEO 170G</t>
+          <t>RC SARDINHA EM OLEO 50X125G</t>
         </is>
       </c>
       <c r="E2237" t="inlineStr">
@@ -76364,7 +76364,7 @@
     <row r="2238">
       <c r="A2238" t="inlineStr">
         <is>
-          <t>90560</t>
+          <t>87088</t>
         </is>
       </c>
       <c r="B2238" t="inlineStr">
@@ -76374,12 +76374,12 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>AGUA LIMPA</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="D2238" t="inlineStr">
         <is>
-          <t>RC SARDINHA EM OLEO 50X125G</t>
+          <t>RC ATUM RALADO EM OLEO 170G</t>
         </is>
       </c>
       <c r="E2238" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="D2310" t="inlineStr">
         <is>
-          <t>VILLA ROSA TINTO 750ML</t>
+          <t>RUM BACARDI SUPERIOR 980ML</t>
         </is>
       </c>
       <c r="E2310" t="inlineStr">
@@ -79336,7 +79336,7 @@
       </c>
       <c r="D2327" t="inlineStr">
         <is>
-          <t>RANCHEIRO WAFER CHOCOLATE 78G</t>
+          <t>4 PACK RED BULL SF POMELO 4X250ML</t>
         </is>
       </c>
       <c r="E2327" t="inlineStr">
@@ -80062,7 +80062,7 @@
       </c>
       <c r="D2349" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL MELÃO C/ MARACUJA</t>
+          <t>RC ATUM PEDACOS NATURAL 170G</t>
         </is>
       </c>
       <c r="E2349" t="inlineStr">
@@ -80293,7 +80293,7 @@
       </c>
       <c r="D2356" t="inlineStr">
         <is>
-          <t>RED BULL 24X250ML</t>
+          <t>RED BULL SF MAÇA 24X250ML</t>
         </is>
       </c>
       <c r="E2356" t="inlineStr">
@@ -83075,7 +83075,7 @@
       </c>
       <c r="D2438" t="inlineStr">
         <is>
-          <t>NG AMOR CARIOCA BOMBOM 500G</t>
+          <t>NG AMOR CARIOCA BOMBOM BRANCO 500G</t>
         </is>
       </c>
       <c r="E2438" t="inlineStr">
@@ -85331,7 +85331,7 @@
       </c>
       <c r="D2506" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL SF MAÇA 4X250ML</t>
         </is>
       </c>
       <c r="E2506" t="inlineStr">
@@ -85529,7 +85529,7 @@
       </c>
       <c r="D2512" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL SF MAÇA 4X250ML</t>
         </is>
       </c>
       <c r="E2512" t="inlineStr">
@@ -86494,7 +86494,7 @@
       </c>
       <c r="D2541" t="inlineStr">
         <is>
-          <t>VINHO VILLA ROSA FRISANTE BRANCO</t>
+          <t>VINHO GRAVEDAD CAB. SAUV./ CARMENERE</t>
         </is>
       </c>
       <c r="E2541" t="inlineStr">
@@ -86527,7 +86527,7 @@
       </c>
       <c r="D2542" t="inlineStr">
         <is>
-          <t>4 PACK RED BULL</t>
+          <t>4 PACK RED BULL SF MAÇA 4X250ML</t>
         </is>
       </c>
       <c r="E2542" t="inlineStr">
@@ -86560,7 +86560,7 @@
       </c>
       <c r="D2543" t="inlineStr">
         <is>
-          <t>RC SARDINHA EM OLEO 125G</t>
+          <t>4 PACK RED BULL ZERO</t>
         </is>
       </c>
       <c r="E2543" t="inlineStr">
@@ -87516,7 +87516,7 @@
       </c>
       <c r="D2571" t="inlineStr">
         <is>
-          <t>VINHO ARESTI ESTATE S. PINOT NOIR</t>
+          <t>VINHO FOODKILLER CAB. SAUV. 750ML</t>
         </is>
       </c>
       <c r="E2571" t="inlineStr">
@@ -89635,7 +89635,7 @@
       </c>
       <c r="D2630" t="inlineStr">
         <is>
-          <t>WHISKY BALLANTINE'S FINEST 750ML</t>
+          <t>RANCHEIRO RECHEADO CHOCOLATE 90G</t>
         </is>
       </c>
       <c r="E2630" t="inlineStr">
